--- a/racecards/racecard_20260613.xlsx
+++ b/racecards/racecard_20260613.xlsx
@@ -739,10 +739,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1026</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -902,7 +904,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>-</t>
@@ -1063,7 +1067,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1006</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1224,10 +1230,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1129</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1391,10 +1399,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1085</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1554,7 +1564,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1715,10 +1727,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1043</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1882,10 +1896,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1191</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2049,10 +2065,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1151</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -2220,10 +2238,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -2391,10 +2411,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1095</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2558,10 +2580,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1112</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2729,10 +2753,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2900,10 +2926,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1058</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -3067,10 +3095,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -3238,10 +3268,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3409,10 +3441,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -3580,10 +3614,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -3751,10 +3787,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>1251</v>
+      </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3896,7 +3934,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -4007,7 +4047,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>1135</v>
+      </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
@@ -4144,10 +4186,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>1032</v>
+      </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -4311,10 +4355,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>1136</v>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -4478,10 +4524,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>1036</v>
+      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -4649,10 +4697,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>1247</v>
+      </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -4820,10 +4870,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>1095</v>
+      </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -4987,10 +5039,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>1187</v>
+      </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -5154,10 +5208,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>1147</v>
+      </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -5321,10 +5377,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
@@ -5488,10 +5546,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>1092</v>
+      </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -5659,10 +5719,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -5826,10 +5888,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>1138</v>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -5993,10 +6057,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -6164,10 +6230,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>1277</v>
+      </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -6335,10 +6403,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>1017</v>
+      </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -6480,7 +6550,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>1179</v>
+      </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
@@ -6587,7 +6659,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>1246</v>
+      </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
@@ -6724,10 +6798,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>1051</v>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -6891,10 +6967,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1057</v>
+      </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -7062,10 +7140,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>1212</v>
+      </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+16</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -7233,10 +7313,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>1070</v>
+      </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -7404,10 +7486,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -7571,10 +7655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>1139</v>
+      </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -7742,10 +7828,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>1017</v>
+      </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -7909,10 +7997,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
@@ -8080,10 +8170,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>1104</v>
+      </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
@@ -8251,10 +8343,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>1068</v>
+      </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -8414,10 +8508,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -8585,10 +8681,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>1206</v>
+      </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -8752,10 +8850,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>1052</v>
+      </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+30</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -8923,10 +9023,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>1204</v>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
@@ -9068,7 +9170,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>1045</v>
+      </c>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
@@ -9179,7 +9283,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>1080</v>
+      </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
@@ -9316,10 +9422,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
@@ -9487,10 +9595,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -9654,10 +9764,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>1255</v>
+      </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -9825,10 +9937,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>1195</v>
+      </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -9996,10 +10110,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>1194</v>
+      </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -10167,10 +10283,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>1067</v>
+      </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -10338,10 +10456,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>1199</v>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
@@ -10505,10 +10625,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
@@ -10676,10 +10798,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>1101</v>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -10843,10 +10967,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -11010,10 +11136,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>1034</v>
+      </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -11181,10 +11309,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -11326,7 +11456,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>1159</v>
+      </c>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
@@ -11437,7 +11569,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>1087</v>
+      </c>
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
@@ -11574,10 +11708,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>1216</v>
+      </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -11745,10 +11881,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
@@ -11916,10 +12054,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>1064</v>
+      </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
@@ -12083,10 +12223,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
@@ -12254,10 +12396,12 @@
           <t>+ 2</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>1012</v>
+      </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr"/>
@@ -12421,10 +12565,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>1166</v>
+      </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -12592,10 +12738,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>1220</v>
+      </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
@@ -12763,10 +12911,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>1033</v>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -12934,10 +13084,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
@@ -13101,10 +13253,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>1088</v>
+      </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr"/>
@@ -13272,10 +13426,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>1033</v>
+      </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -13439,10 +13595,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr"/>
@@ -13606,10 +13764,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
@@ -13781,10 +13941,12 @@
           <t>+ * 2</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>1117</v>
+      </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -13922,7 +14084,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>1076</v>
+      </c>
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
@@ -14033,7 +14197,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
@@ -14170,10 +14336,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -14341,10 +14509,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>1165</v>
+      </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
@@ -14512,10 +14682,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>1145</v>
+      </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -14683,10 +14855,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>1125</v>
+      </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -14854,10 +15028,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>1298</v>
+      </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
@@ -15025,10 +15201,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>1104</v>
+      </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -15192,10 +15370,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr"/>
+      <c r="AC91" t="n">
+        <v>1065</v>
+      </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
@@ -15359,7 +15539,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD92" t="inlineStr">
         <is>
           <t>-</t>
@@ -15520,7 +15702,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr"/>
+      <c r="AC93" t="n">
+        <v>971</v>
+      </c>
       <c r="AD93" t="inlineStr">
         <is>
           <t>-</t>
@@ -15685,10 +15869,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr"/>
+      <c r="AC94" t="n">
+        <v>1036</v>
+      </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -15856,10 +16042,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr"/>
+      <c r="AC95" t="n">
+        <v>1032</v>
+      </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr"/>
@@ -16023,10 +16211,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr"/>
+      <c r="AC96" t="n">
+        <v>1015</v>
+      </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -16168,7 +16358,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>1052</v>
+      </c>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
@@ -16279,7 +16471,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD98" t="inlineStr"/>
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
@@ -16416,10 +16610,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>1041</v>
+      </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
@@ -16587,10 +16783,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
@@ -16758,10 +16956,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr"/>
+      <c r="AC101" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
@@ -16929,10 +17129,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>1072</v>
+      </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
@@ -17100,10 +17302,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>1120</v>
+      </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
@@ -17267,10 +17471,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>1080</v>
+      </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
@@ -17434,10 +17640,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>1232</v>
+      </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
@@ -17605,10 +17813,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>1147</v>
+      </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
@@ -17772,10 +17982,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>1034</v>
+      </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+23</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr"/>
@@ -17935,10 +18147,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>1080</v>
+      </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -18106,10 +18320,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr"/>
+      <c r="AC109" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
@@ -18277,10 +18493,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr"/>
+      <c r="AC110" t="n">
+        <v>1278</v>
+      </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
@@ -18444,10 +18662,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr"/>
+      <c r="AC111" t="n">
+        <v>1064</v>
+      </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr"/>
@@ -18611,10 +18831,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr"/>
+      <c r="AC112" t="n">
+        <v>1237</v>
+      </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -18782,10 +19004,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr"/>
+      <c r="AC113" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
@@ -18953,10 +19177,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr"/>
+      <c r="AC114" t="n">
+        <v>1072</v>
+      </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr"/>
@@ -19120,7 +19346,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr"/>
+      <c r="AC115" t="n">
+        <v>1074</v>
+      </c>
       <c r="AD115" t="inlineStr">
         <is>
           <t>-</t>
@@ -19285,10 +19513,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr"/>
+      <c r="AC116" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
@@ -19456,10 +19686,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr"/>
+      <c r="AC117" t="n">
+        <v>1190</v>
+      </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
@@ -19627,10 +19859,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr"/>
+      <c r="AC118" t="n">
+        <v>1196</v>
+      </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
@@ -19798,10 +20032,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr"/>
+      <c r="AC119" t="n">
+        <v>1094</v>
+      </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
@@ -19969,10 +20205,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr"/>
+      <c r="AC120" t="n">
+        <v>1175</v>
+      </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -20114,7 +20352,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr"/>
+      <c r="AC121" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD121" t="inlineStr"/>
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
@@ -20225,7 +20465,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr"/>
+      <c r="AC122" t="n">
+        <v>1157</v>
+      </c>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
@@ -20362,10 +20604,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr"/>
+      <c r="AC123" t="n">
+        <v>1058</v>
+      </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
@@ -20533,10 +20777,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr"/>
+      <c r="AC124" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -20704,10 +20950,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr"/>
+      <c r="AC125" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -20871,10 +21119,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr"/>
+      <c r="AC126" t="n">
+        <v>1095</v>
+      </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
@@ -21042,10 +21292,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr"/>
+      <c r="AC127" t="n">
+        <v>1113</v>
+      </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -21213,10 +21465,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr"/>
+      <c r="AC128" t="n">
+        <v>1231</v>
+      </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr"/>
@@ -21380,10 +21634,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr"/>
+      <c r="AC129" t="n">
+        <v>1182</v>
+      </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
@@ -21551,10 +21807,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr"/>
+      <c r="AC130" t="n">
+        <v>1108</v>
+      </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -21722,10 +21980,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr"/>
+      <c r="AC131" t="n">
+        <v>1266</v>
+      </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr"/>
@@ -21889,10 +22149,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr"/>
+      <c r="AC132" t="n">
+        <v>1159</v>
+      </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
@@ -22060,10 +22322,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr"/>
+      <c r="AC133" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
@@ -22235,10 +22499,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>1094</v>
+      </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr"/>
@@ -22402,10 +22668,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr"/>
@@ -22569,10 +22837,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr"/>
+      <c r="AC136" t="n">
+        <v>1219</v>
+      </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
@@ -22714,7 +22984,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr"/>
+      <c r="AC137" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
@@ -22821,7 +23093,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr"/>
+      <c r="AC138" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD138" t="inlineStr"/>
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
@@ -22962,10 +23236,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr"/>
+      <c r="AC139" t="n">
+        <v>1063</v>
+      </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr"/>
@@ -23133,10 +23409,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr"/>
+      <c r="AC140" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
@@ -23308,10 +23586,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>1122</v>
+      </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
@@ -23483,10 +23763,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr"/>
+      <c r="AC142" t="n">
+        <v>1149</v>
+      </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
@@ -23658,10 +23940,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>1077</v>
+      </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
@@ -23833,7 +24117,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr"/>
+      <c r="AC144" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD144" t="inlineStr">
         <is>
           <t>-</t>
@@ -24002,10 +24288,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr"/>
+      <c r="AC145" t="n">
+        <v>1130</v>
+      </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
@@ -24173,10 +24461,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>1133</v>
+      </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
@@ -24348,10 +24638,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr"/>
+      <c r="AC147" t="n">
+        <v>1085</v>
+      </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
@@ -24523,10 +24815,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr"/>
+      <c r="AC148" t="n">
+        <v>1152</v>
+      </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
@@ -24694,10 +24988,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr"/>
+      <c r="AC149" t="n">
+        <v>1220</v>
+      </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr"/>
@@ -24865,10 +25161,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr"/>
+      <c r="AC150" t="n">
+        <v>1165</v>
+      </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
@@ -25040,10 +25338,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
@@ -25215,10 +25515,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr"/>
+      <c r="AC152" t="n">
+        <v>1169</v>
+      </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
@@ -25364,7 +25666,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr"/>
+      <c r="AC153" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD153" t="inlineStr"/>
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
@@ -25479,7 +25783,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr"/>
+      <c r="AC154" t="n">
+        <v>1207</v>
+      </c>
       <c r="AD154" t="inlineStr"/>
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
@@ -25837,10 +26143,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -26008,10 +26316,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1278</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -26175,10 +26485,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1064</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -26342,10 +26654,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1237</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -26513,10 +26827,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -26684,10 +27000,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1072</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -26851,7 +27169,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1074</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>-</t>
@@ -27016,10 +27336,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -27187,10 +27509,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1190</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -27358,10 +27682,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1196</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -27529,10 +27855,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1094</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -27700,10 +28028,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1175</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -27845,7 +28175,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -27956,7 +28288,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1157</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -28314,10 +28648,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1058</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -28485,10 +28821,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -28656,10 +28994,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -28823,10 +29163,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1095</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -28994,10 +29336,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1113</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -29165,10 +29509,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1231</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -29332,10 +29678,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1182</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -29503,10 +29851,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1108</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -29674,10 +30024,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1266</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -29841,10 +30193,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1159</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -30012,10 +30366,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -30187,10 +30543,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1094</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -30354,10 +30712,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -30521,10 +30881,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1219</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -30666,7 +31028,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -30773,7 +31137,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -31135,10 +31501,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1063</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -31306,10 +31674,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -31481,10 +31851,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1122</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -31656,10 +32028,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1149</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -31831,10 +32205,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1077</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -32006,7 +32382,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>-</t>
@@ -32175,10 +32553,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1130</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -32346,10 +32726,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1133</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -32521,10 +32903,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1085</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -32696,10 +33080,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1152</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -32867,10 +33253,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1220</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -33038,10 +33426,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1165</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -33213,10 +33603,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -33388,10 +33780,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1169</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -33537,7 +33931,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -33652,7 +34048,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1207</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -34002,10 +34400,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1026</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -34165,7 +34565,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>-</t>
@@ -34326,7 +34728,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1006</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>-</t>
@@ -34487,10 +34891,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1129</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -34654,10 +35060,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1085</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -34817,7 +35225,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>-</t>
@@ -34978,10 +35388,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1043</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -35366,10 +35778,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1191</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -35533,10 +35947,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1151</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -35704,10 +36120,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -35875,10 +36293,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1095</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -36042,10 +36462,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1112</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -36213,10 +36635,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -36384,10 +36808,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1058</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -36551,10 +36977,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -36722,10 +37150,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -36893,10 +37323,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -37064,10 +37496,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -37235,10 +37669,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1251</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -37380,7 +37816,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -37491,7 +37929,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1135</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -37849,10 +38289,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1032</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -38016,10 +38458,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1136</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -38183,10 +38627,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1036</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -38354,10 +38800,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1247</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -38525,10 +38973,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1095</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -38692,10 +39142,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1187</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -38859,10 +39311,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1147</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -39026,10 +39480,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -39193,10 +39649,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1092</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -39364,10 +39822,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -39531,10 +39991,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1138</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -39698,10 +40160,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -39869,10 +40333,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1277</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -40040,10 +40506,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1017</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -40185,7 +40653,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1179</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -40292,7 +40762,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1246</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -40650,10 +41122,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1051</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -40817,10 +41291,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1057</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -40988,10 +41464,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1212</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -41159,10 +41637,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1070</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -41330,10 +41810,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -41497,10 +41979,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1139</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -41668,10 +42152,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1017</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -41835,10 +42321,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -42006,10 +42494,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1104</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -42177,10 +42667,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1068</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -42340,10 +42832,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -42511,10 +43005,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1206</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -42678,10 +43174,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1052</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+30</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -42849,10 +43347,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1204</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -42994,7 +43494,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1045</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -43105,7 +43607,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1080</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -43463,10 +43967,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -43634,10 +44140,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -43801,10 +44309,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1255</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -43972,10 +44482,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1195</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -44143,10 +44655,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1194</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -44314,10 +44828,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1067</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -44485,10 +45001,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1199</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -44652,10 +45170,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -44823,10 +45343,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1101</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -44990,10 +45512,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -45157,10 +45681,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1034</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -45328,10 +45854,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -45473,7 +46001,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1159</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -45584,7 +46114,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1087</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -45942,10 +46474,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1216</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -46113,10 +46647,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -46284,10 +46820,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1064</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -46451,10 +46989,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -46622,10 +47162,12 @@
           <t>+ 2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1012</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -46789,10 +47331,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1166</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -46960,10 +47504,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1220</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -47131,10 +47677,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1033</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -47302,10 +47850,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -47469,10 +48019,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1088</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -47640,10 +48192,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1033</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -47807,10 +48361,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -47974,10 +48530,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -48149,10 +48707,12 @@
           <t>+ * 2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1117</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -48290,7 +48850,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1076</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -48401,7 +48963,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -48759,10 +49323,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -48930,10 +49496,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1165</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -49101,10 +49669,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1145</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -49272,10 +49842,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1125</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -49443,10 +50015,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1298</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -49614,10 +50188,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1104</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -49781,10 +50357,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1065</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -49948,7 +50526,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>-</t>
@@ -50109,7 +50689,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>971</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>-</t>
@@ -50274,10 +50856,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1036</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -50445,10 +51029,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1032</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -50612,10 +51198,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1015</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -50757,7 +51345,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1052</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -50868,7 +51458,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -51226,10 +51818,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1041</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -51397,10 +51991,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -51568,10 +52164,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -51739,10 +52337,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1072</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -51910,10 +52510,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1120</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -52077,10 +52679,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1080</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -52244,10 +52848,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1232</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -52415,10 +53021,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1147</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -52582,10 +53190,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1034</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+23</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -52745,10 +53355,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1080</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
